--- a/artfynd/A 21610-2026 artfynd.xlsx
+++ b/artfynd/A 21610-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136806232</v>
       </c>
       <c r="B2" t="n">
-        <v>58552</v>
+        <v>58565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136806519</v>
       </c>
       <c r="B3" t="n">
-        <v>58552</v>
+        <v>58565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136806117</v>
       </c>
       <c r="B4" t="n">
-        <v>58448</v>
+        <v>58461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136806230</v>
       </c>
       <c r="B5" t="n">
-        <v>58443</v>
+        <v>58456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136806234</v>
       </c>
       <c r="B6" t="n">
-        <v>58443</v>
+        <v>58456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136806237</v>
       </c>
       <c r="B7" t="n">
-        <v>58443</v>
+        <v>58456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136806357</v>
       </c>
       <c r="B8" t="n">
-        <v>58443</v>
+        <v>58456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136806462</v>
       </c>
       <c r="B9" t="n">
-        <v>58443</v>
+        <v>58456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136806591</v>
       </c>
       <c r="B10" t="n">
-        <v>58443</v>
+        <v>58456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>136806587</v>
       </c>
       <c r="B11" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136806458</v>
       </c>
       <c r="B12" t="n">
-        <v>58667</v>
+        <v>58680</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 21610-2026 artfynd.xlsx
+++ b/artfynd/A 21610-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136806232</v>
       </c>
       <c r="B2" t="n">
-        <v>58565</v>
+        <v>58567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136806519</v>
       </c>
       <c r="B3" t="n">
-        <v>58565</v>
+        <v>58567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136806117</v>
       </c>
       <c r="B4" t="n">
-        <v>58461</v>
+        <v>58463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136806230</v>
       </c>
       <c r="B5" t="n">
-        <v>58456</v>
+        <v>58458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136806234</v>
       </c>
       <c r="B6" t="n">
-        <v>58456</v>
+        <v>58458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136806237</v>
       </c>
       <c r="B7" t="n">
-        <v>58456</v>
+        <v>58458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136806357</v>
       </c>
       <c r="B8" t="n">
-        <v>58456</v>
+        <v>58458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136806462</v>
       </c>
       <c r="B9" t="n">
-        <v>58456</v>
+        <v>58458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136806591</v>
       </c>
       <c r="B10" t="n">
-        <v>58456</v>
+        <v>58458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>136806587</v>
       </c>
       <c r="B11" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136806458</v>
       </c>
       <c r="B12" t="n">
-        <v>58680</v>
+        <v>58682</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 21610-2026 artfynd.xlsx
+++ b/artfynd/A 21610-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136806232</v>
       </c>
       <c r="B2" t="n">
-        <v>58567</v>
+        <v>58577</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136806519</v>
       </c>
       <c r="B3" t="n">
-        <v>58567</v>
+        <v>58577</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136806117</v>
       </c>
       <c r="B4" t="n">
-        <v>58463</v>
+        <v>58473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136806230</v>
       </c>
       <c r="B5" t="n">
-        <v>58458</v>
+        <v>58468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136806234</v>
       </c>
       <c r="B6" t="n">
-        <v>58458</v>
+        <v>58468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136806237</v>
       </c>
       <c r="B7" t="n">
-        <v>58458</v>
+        <v>58468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136806357</v>
       </c>
       <c r="B8" t="n">
-        <v>58458</v>
+        <v>58468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136806462</v>
       </c>
       <c r="B9" t="n">
-        <v>58458</v>
+        <v>58468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136806591</v>
       </c>
       <c r="B10" t="n">
-        <v>58458</v>
+        <v>58468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>136806587</v>
       </c>
       <c r="B11" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136806458</v>
       </c>
       <c r="B12" t="n">
-        <v>58682</v>
+        <v>58692</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 21610-2026 artfynd.xlsx
+++ b/artfynd/A 21610-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136806232</v>
       </c>
       <c r="B2" t="n">
-        <v>58577</v>
+        <v>58579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136806519</v>
       </c>
       <c r="B3" t="n">
-        <v>58577</v>
+        <v>58579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136806117</v>
       </c>
       <c r="B4" t="n">
-        <v>58473</v>
+        <v>58474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136806230</v>
       </c>
       <c r="B5" t="n">
-        <v>58468</v>
+        <v>58469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136806234</v>
       </c>
       <c r="B6" t="n">
-        <v>58468</v>
+        <v>58469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136806237</v>
       </c>
       <c r="B7" t="n">
-        <v>58468</v>
+        <v>58469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136806357</v>
       </c>
       <c r="B8" t="n">
-        <v>58468</v>
+        <v>58469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136806462</v>
       </c>
       <c r="B9" t="n">
-        <v>58468</v>
+        <v>58469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136806591</v>
       </c>
       <c r="B10" t="n">
-        <v>58468</v>
+        <v>58469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>136806587</v>
       </c>
       <c r="B11" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136806458</v>
       </c>
       <c r="B12" t="n">
-        <v>58692</v>
+        <v>58694</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 21610-2026 artfynd.xlsx
+++ b/artfynd/A 21610-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136806232</v>
       </c>
       <c r="B2" t="n">
-        <v>58579</v>
+        <v>58581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136806519</v>
       </c>
       <c r="B3" t="n">
-        <v>58579</v>
+        <v>58581</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136806117</v>
       </c>
       <c r="B4" t="n">
-        <v>58474</v>
+        <v>58476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136806230</v>
       </c>
       <c r="B5" t="n">
-        <v>58469</v>
+        <v>58471</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136806234</v>
       </c>
       <c r="B6" t="n">
-        <v>58469</v>
+        <v>58471</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136806237</v>
       </c>
       <c r="B7" t="n">
-        <v>58469</v>
+        <v>58471</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136806357</v>
       </c>
       <c r="B8" t="n">
-        <v>58469</v>
+        <v>58471</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136806462</v>
       </c>
       <c r="B9" t="n">
-        <v>58469</v>
+        <v>58471</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136806591</v>
       </c>
       <c r="B10" t="n">
-        <v>58469</v>
+        <v>58471</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>136806587</v>
       </c>
       <c r="B11" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136806458</v>
       </c>
       <c r="B12" t="n">
-        <v>58694</v>
+        <v>58696</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
